--- a/data/Survey about marriage.xlsx
+++ b/data/Survey about marriage.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mega Pc\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mega Pc\OneDrive\Desktop\Survey mini project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCC21704-6421-4700-BB32-CD58C6D9C6CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31652189-35D3-422B-9E4E-B3E7AE9710BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,60 +45,9 @@
     <t>Gender</t>
   </si>
   <si>
-    <t>Are you married ?</t>
-  </si>
-  <si>
-    <t>If no, are you planning to get married ? (optional)</t>
-  </si>
-  <si>
-    <t>In your opinion, what is the ideal age to get married for a woman ?</t>
-  </si>
-  <si>
-    <t>In your opinion, what is the ideal age to get married for a man ?</t>
-  </si>
-  <si>
-    <t>On a scale from 1 to 5, how important is marriage in your opinion ?</t>
-  </si>
-  <si>
-    <t>Preferred partner height</t>
-  </si>
-  <si>
-    <t>Most important qualities in a partner (Choose up to 3)</t>
-  </si>
-  <si>
-    <t>Do you want children ?</t>
-  </si>
-  <si>
-    <t>Ideal number of children </t>
-  </si>
-  <si>
-    <t>Ideal age to have the first child</t>
-  </si>
-  <si>
-    <t>Preferred household financial model</t>
-  </si>
-  <si>
-    <t>How important is financial transparency between spouses?</t>
-  </si>
-  <si>
-    <t>Is it important that both partners work ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How should household chores and responsibilities generally be divided in a marriage?  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">What is the biggest challenge facing married couples in your generation ?  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">After marriage, which living arrangement do you prefer ?  </t>
-  </si>
-  <si>
     <t>Impact</t>
   </si>
   <si>
-    <t xml:space="preserve">Which factor do you believe is most important for a successful marriage ?  </t>
-  </si>
-  <si>
     <t>anonymous</t>
   </si>
   <si>
@@ -499,6 +448,57 @@
   </si>
   <si>
     <t>27-33</t>
+  </si>
+  <si>
+    <t>marital_status</t>
+  </si>
+  <si>
+    <t>marriage_planning</t>
+  </si>
+  <si>
+    <t>ideal_age_woman</t>
+  </si>
+  <si>
+    <t>ideal_age_man</t>
+  </si>
+  <si>
+    <t>marriage_importance</t>
+  </si>
+  <si>
+    <t>height_preference</t>
+  </si>
+  <si>
+    <t>important_qualities</t>
+  </si>
+  <si>
+    <t>children_want</t>
+  </si>
+  <si>
+    <t>ideal_children_number</t>
+  </si>
+  <si>
+    <t>ideal_age_first_child</t>
+  </si>
+  <si>
+    <t>financial_model</t>
+  </si>
+  <si>
+    <t>financial_transparency</t>
+  </si>
+  <si>
+    <t>both_work</t>
+  </si>
+  <si>
+    <t>household_chores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">biggest_challenge </t>
+  </si>
+  <si>
+    <t>living_arrangment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">successful_marriage </t>
   </si>
 </sst>
 </file>
@@ -506,7 +506,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="m/d/yy\ h:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -539,7 +539,7 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -610,10 +610,10 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="m/d/yy\ h:mm:ss"/>
+      <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="m/d/yy\ h:mm:ss"/>
+      <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -641,24 +641,24 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Email" dataDxfId="20"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Age" dataDxfId="19"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Gender" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Are you married ?" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="If no, are you planning to get married ? (optional)" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="In your opinion, what is the ideal age to get married for a woman ?" dataDxfId="15"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="In your opinion, what is the ideal age to get married for a man ?" dataDxfId="14"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="On a scale from 1 to 5, how important is marriage in your opinion ?" dataDxfId="13"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Preferred partner height" dataDxfId="12"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Most important qualities in a partner (Choose up to 3)" dataDxfId="11"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Do you want children ?" dataDxfId="10"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Ideal number of children " dataDxfId="9"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Ideal age to have the first child" dataDxfId="8"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Preferred household financial model" dataDxfId="7"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="How important is financial transparency between spouses?" dataDxfId="6"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Is it important that both partners work ?" dataDxfId="5"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="How should household chores and responsibilities generally be divided in a marriage?  " dataDxfId="4"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="What is the biggest challenge facing married couples in your generation ?  " dataDxfId="3"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="After marriage, which living arrangement do you prefer ?  " dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="marital_status" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="marriage_planning" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="ideal_age_woman" dataDxfId="15"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="ideal_age_man" dataDxfId="14"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="marriage_importance" dataDxfId="13"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="height_preference" dataDxfId="12"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="important_qualities" dataDxfId="11"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="children_want" dataDxfId="10"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="ideal_children_number" dataDxfId="9"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="ideal_age_first_child" dataDxfId="8"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="financial_model" dataDxfId="7"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="financial_transparency" dataDxfId="6"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="both_work" dataDxfId="5"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="household_chores" dataDxfId="4"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="biggest_challenge " dataDxfId="3"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="living_arrangment" dataDxfId="2"/>
     <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Impact" dataDxfId="1"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Which factor do you believe is most important for a successful marriage ?  " dataDxfId="0"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="successful_marriage " dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -997,58 +997,58 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I1" t="s">
+        <v>143</v>
+      </c>
+      <c r="J1" t="s">
+        <v>144</v>
+      </c>
+      <c r="K1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L1" t="s">
+        <v>146</v>
+      </c>
+      <c r="M1" t="s">
+        <v>147</v>
+      </c>
+      <c r="N1" t="s">
+        <v>148</v>
+      </c>
+      <c r="O1" t="s">
+        <v>149</v>
+      </c>
+      <c r="P1" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>151</v>
+      </c>
+      <c r="R1" t="s">
+        <v>152</v>
+      </c>
+      <c r="S1" t="s">
+        <v>153</v>
+      </c>
+      <c r="T1" t="s">
+        <v>154</v>
+      </c>
+      <c r="U1" t="s">
+        <v>155</v>
+      </c>
+      <c r="V1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" t="s">
-        <v>22</v>
-      </c>
       <c r="X1" t="s">
-        <v>23</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
@@ -1062,67 +1062,67 @@
         <v>46005.893576388902</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H2" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="K2">
         <v>5</v>
       </c>
       <c r="L2" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="M2" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="N2" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="Q2" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="R2" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S2">
         <v>5</v>
       </c>
       <c r="T2" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="U2" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="V2" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="W2" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="X2" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
@@ -1136,67 +1136,67 @@
         <v>46005.894733796304</v>
       </c>
       <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="F3" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H3" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="K3">
         <v>5</v>
       </c>
       <c r="L3" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="M3" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="N3" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="Q3" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="R3" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S3">
         <v>3</v>
       </c>
       <c r="T3" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="U3" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="V3" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W3" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="X3" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
@@ -1210,64 +1210,64 @@
         <v>46005.902071759301</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="F4" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="K4">
         <v>5</v>
       </c>
       <c r="L4" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="M4" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="N4" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="Q4" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="R4" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S4">
         <v>4</v>
       </c>
       <c r="T4" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="U4" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="V4" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W4" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="X4" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
@@ -1281,67 +1281,67 @@
         <v>46005.9041782407</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" t="s">
         <v>42</v>
       </c>
-      <c r="G5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" t="s">
-        <v>59</v>
-      </c>
       <c r="J5" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="K5">
         <v>4</v>
       </c>
       <c r="L5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5" t="s">
         <v>44</v>
       </c>
-      <c r="M5" t="s">
-        <v>61</v>
-      </c>
       <c r="N5" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="P5" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="Q5" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="R5" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S5">
         <v>3</v>
       </c>
       <c r="T5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="U5" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="V5" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W5" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="X5" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
@@ -1355,64 +1355,64 @@
         <v>46005.905960648102</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="F6" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="K6">
         <v>3</v>
       </c>
       <c r="L6" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="M6" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="N6" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="Q6" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="R6" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S6">
         <v>5</v>
       </c>
       <c r="T6" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="U6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="V6" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W6" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="X6" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
@@ -1426,67 +1426,67 @@
         <v>46005.909710648099</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H7" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="K7">
         <v>1</v>
       </c>
       <c r="L7" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="M7" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="N7" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="Q7" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="R7" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S7">
         <v>5</v>
       </c>
       <c r="T7" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="U7" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="V7" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="W7" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="X7" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
@@ -1500,64 +1500,64 @@
         <v>46005.910057870402</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="F8" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G8" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="K8">
         <v>5</v>
       </c>
       <c r="L8" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="M8" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="N8" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="Q8" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="R8" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="S8">
         <v>2</v>
       </c>
       <c r="T8" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="U8" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="V8" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="W8" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="X8" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
@@ -1571,67 +1571,67 @@
         <v>46005.913113425901</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="F9" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G9" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H9" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="J9" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="K9">
         <v>4</v>
       </c>
       <c r="L9" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="M9" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="N9" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="Q9" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="R9" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="S9">
         <v>3</v>
       </c>
       <c r="T9" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="U9" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="V9" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W9" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="X9" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
@@ -1645,67 +1645,67 @@
         <v>46005.914340277799</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G10" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H10" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I10" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J10" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="K10">
         <v>3</v>
       </c>
       <c r="L10" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="M10" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="N10" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="Q10" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="R10" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S10">
         <v>5</v>
       </c>
       <c r="T10" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="U10" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="V10" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="W10" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="X10" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
@@ -1719,67 +1719,67 @@
         <v>46005.9155439815</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H11" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="K11">
         <v>3</v>
       </c>
       <c r="L11" t="s">
+        <v>14</v>
+      </c>
+      <c r="M11" t="s">
+        <v>67</v>
+      </c>
+      <c r="N11" t="s">
+        <v>11</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q11" t="s">
         <v>31</v>
       </c>
-      <c r="M11" t="s">
-        <v>84</v>
-      </c>
-      <c r="N11" t="s">
-        <v>28</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>48</v>
-      </c>
       <c r="R11" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="S11">
         <v>3</v>
       </c>
       <c r="T11" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="U11" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="V11" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="W11" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="X11" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
@@ -1793,67 +1793,67 @@
         <v>46005.917187500003</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G12" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H12" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I12" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="J12" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="K12">
         <v>4</v>
       </c>
       <c r="L12" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="M12" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="N12" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="Q12" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="R12" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S12">
         <v>4</v>
       </c>
       <c r="T12" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="U12" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="V12" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W12" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="X12" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
@@ -1867,67 +1867,67 @@
         <v>46005.918958333299</v>
       </c>
       <c r="D13" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G13" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H13" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I13" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="J13" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="K13">
         <v>4</v>
       </c>
       <c r="L13" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="M13" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="N13" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="P13" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="Q13" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="R13" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S13">
         <v>4</v>
       </c>
       <c r="T13" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="U13" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="V13" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W13" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="X13" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
@@ -1941,67 +1941,67 @@
         <v>46005.919027777803</v>
       </c>
       <c r="D14" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="F14" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G14" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H14" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="K14">
         <v>4</v>
       </c>
       <c r="L14" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="M14" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="N14" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="Q14" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="R14" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S14">
         <v>3</v>
       </c>
       <c r="T14" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="U14" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="V14" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="W14" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="X14" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
@@ -2015,67 +2015,67 @@
         <v>46005.924525463</v>
       </c>
       <c r="D15" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F15" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G15" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H15" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I15" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="K15">
         <v>5</v>
       </c>
       <c r="L15" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="M15" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="N15" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="Q15" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="R15" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="S15">
         <v>3</v>
       </c>
       <c r="T15" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="U15" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="V15" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W15" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="X15" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
@@ -2089,67 +2089,67 @@
         <v>46005.928796296299</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="F16" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G16" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H16" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="K16">
         <v>5</v>
       </c>
       <c r="L16" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="M16" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="N16" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="Q16" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="R16" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="S16">
         <v>3</v>
       </c>
       <c r="T16" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="U16" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="V16" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W16" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="X16" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.3">
@@ -2163,64 +2163,64 @@
         <v>46005.937789351803</v>
       </c>
       <c r="D17" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
         <v>25</v>
       </c>
-      <c r="F17" t="s">
-        <v>42</v>
-      </c>
       <c r="G17" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="K17">
         <v>5</v>
       </c>
       <c r="L17" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="M17" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="N17" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="Q17" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="R17" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S17">
         <v>3</v>
       </c>
       <c r="T17" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="U17" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="V17" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="W17" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="X17" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.3">
@@ -2234,67 +2234,67 @@
         <v>46005.940729166701</v>
       </c>
       <c r="D18" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="F18" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G18" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H18" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="K18">
         <v>4</v>
       </c>
       <c r="L18" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="M18" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="N18" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="Q18" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="R18" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="S18">
         <v>1</v>
       </c>
       <c r="T18" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="U18" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="V18" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="W18" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="X18" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.3">
@@ -2308,67 +2308,67 @@
         <v>46005.9433796296</v>
       </c>
       <c r="D19" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="F19" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G19" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H19" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="K19">
         <v>3</v>
       </c>
       <c r="L19" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="M19" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="N19" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="Q19" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="R19" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="S19">
         <v>3</v>
       </c>
       <c r="T19" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="U19" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="V19" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W19" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="X19" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.3">
@@ -2382,64 +2382,64 @@
         <v>46005.946944444397</v>
       </c>
       <c r="D20" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="F20" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G20" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="K20">
         <v>5</v>
       </c>
       <c r="L20" t="s">
+        <v>14</v>
+      </c>
+      <c r="M20" t="s">
+        <v>75</v>
+      </c>
+      <c r="N20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q20" t="s">
         <v>31</v>
       </c>
-      <c r="M20" t="s">
-        <v>92</v>
-      </c>
-      <c r="N20" t="s">
-        <v>28</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>48</v>
-      </c>
       <c r="R20" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="S20">
         <v>2</v>
       </c>
       <c r="T20" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="U20" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="V20" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W20" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="X20" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.3">
@@ -2453,67 +2453,67 @@
         <v>46005.950138888897</v>
       </c>
       <c r="D21" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F21" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G21" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H21" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K21">
         <v>5</v>
       </c>
       <c r="L21" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="M21" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="N21" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="Q21" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="R21" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S21">
         <v>4</v>
       </c>
       <c r="T21" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="U21" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="V21" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W21" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="X21" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.3">
@@ -2527,67 +2527,67 @@
         <v>46005.953101851803</v>
       </c>
       <c r="D22" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F22" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G22" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H22" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="K22">
         <v>4</v>
       </c>
       <c r="L22" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="M22" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="N22" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="Q22" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="R22" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="S22">
         <v>4</v>
       </c>
       <c r="T22" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="U22" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="V22" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="W22" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="X22" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.3">
@@ -2601,67 +2601,67 @@
         <v>46005.974166666703</v>
       </c>
       <c r="D23" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="F23" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G23" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H23" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="K23">
         <v>4</v>
       </c>
       <c r="L23" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="M23" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="N23" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="Q23" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="R23" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S23">
         <v>5</v>
       </c>
       <c r="T23" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="U23" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="V23" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="W23" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="X23" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.3">
@@ -2675,67 +2675,67 @@
         <v>46006.369791666701</v>
       </c>
       <c r="D24" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
         <v>25</v>
       </c>
-      <c r="F24" t="s">
-        <v>42</v>
-      </c>
       <c r="G24" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H24" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="K24">
         <v>5</v>
       </c>
       <c r="L24" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="M24" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="N24" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="Q24" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="R24" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S24">
         <v>3</v>
       </c>
       <c r="T24" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="U24" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="V24" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="W24" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="X24" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.3">
@@ -2749,67 +2749,67 @@
         <v>46006.429050925901</v>
       </c>
       <c r="D25" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="F25" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G25" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H25" t="s">
+        <v>73</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J25" t="s">
         <v>90</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="J25" t="s">
-        <v>107</v>
       </c>
       <c r="K25">
         <v>4</v>
       </c>
       <c r="L25" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="M25" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="N25" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="Q25" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="R25" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S25">
         <v>4</v>
       </c>
       <c r="T25" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="U25" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="V25" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W25" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="X25" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.3">
@@ -2823,67 +2823,67 @@
         <v>46006.431157407402</v>
       </c>
       <c r="D26" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F26" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G26" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H26" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="K26">
         <v>4</v>
       </c>
       <c r="L26" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="M26" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="N26" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="Q26" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="R26" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="S26">
         <v>5</v>
       </c>
       <c r="T26" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="U26" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="V26" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W26" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="X26" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.3">
@@ -2897,64 +2897,64 @@
         <v>46006.444305555597</v>
       </c>
       <c r="D27" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="F27" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G27" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I27" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="J27" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="K27">
         <v>5</v>
       </c>
       <c r="L27" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="M27" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="N27" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="Q27" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="R27" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S27">
         <v>5</v>
       </c>
       <c r="T27" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="U27" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="V27" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="W27" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="X27" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.3">
@@ -2968,67 +2968,67 @@
         <v>46006.463530092602</v>
       </c>
       <c r="D28" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F28" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G28" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H28" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="K28">
         <v>4</v>
       </c>
       <c r="L28" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="M28" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="N28" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="Q28" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="R28" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S28">
         <v>4</v>
       </c>
       <c r="T28" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="U28" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="V28" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W28" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="X28" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.3">
@@ -3042,67 +3042,67 @@
         <v>46006.486770833297</v>
       </c>
       <c r="D29" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F29" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G29" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H29" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="K29">
         <v>5</v>
       </c>
       <c r="L29" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="M29" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="N29" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="Q29" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="R29" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="S29">
         <v>2</v>
       </c>
       <c r="T29" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="U29" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="V29" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="W29" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="X29" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.3">
@@ -3116,67 +3116,67 @@
         <v>46006.487060185202</v>
       </c>
       <c r="D30" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="F30" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G30" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H30" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="K30">
         <v>5</v>
       </c>
       <c r="L30" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="M30" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="N30" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="Q30" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="R30" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="S30">
         <v>1</v>
       </c>
       <c r="T30" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="U30" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="V30" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="W30" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="X30" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.3">
@@ -3190,67 +3190,67 @@
         <v>46006.551435185203</v>
       </c>
       <c r="D31" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F31" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G31" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H31" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="K31">
         <v>3</v>
       </c>
       <c r="L31" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="M31" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="N31" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="Q31" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="R31" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S31">
         <v>4</v>
       </c>
       <c r="T31" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="U31" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="V31" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W31" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="X31" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.3">
@@ -3264,67 +3264,67 @@
         <v>46006.8824074074</v>
       </c>
       <c r="D32" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E32" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" t="s">
+        <v>9</v>
+      </c>
+      <c r="G32" t="s">
+        <v>11</v>
+      </c>
+      <c r="H32" t="s">
+        <v>11</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J32" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="F32" t="s">
-        <v>26</v>
-      </c>
-      <c r="G32" t="s">
-        <v>28</v>
-      </c>
-      <c r="H32" t="s">
-        <v>28</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="K32">
         <v>4</v>
       </c>
       <c r="L32" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="M32" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="N32" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="Q32" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="R32" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="S32">
         <v>5</v>
       </c>
       <c r="T32" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="U32" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="V32" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="W32" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="X32" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.3">
@@ -3338,64 +3338,64 @@
         <v>46006.883692129602</v>
       </c>
       <c r="D33" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="F33" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G33" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="K33">
         <v>3</v>
       </c>
       <c r="L33" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="M33" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="N33" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="Q33" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="R33" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S33">
         <v>3</v>
       </c>
       <c r="T33" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="U33" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="V33" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W33" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="X33" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.3">
@@ -3409,67 +3409,67 @@
         <v>46006.885405092602</v>
       </c>
       <c r="D34" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="F34" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G34" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H34" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="K34">
         <v>5</v>
       </c>
       <c r="L34" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="M34" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="N34" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="Q34" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="R34" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S34">
         <v>5</v>
       </c>
       <c r="T34" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="U34" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="V34" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W34" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="X34" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.3">
@@ -3483,67 +3483,67 @@
         <v>46007.569444444402</v>
       </c>
       <c r="D35" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="F35" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G35" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H35" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I35" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="K35">
         <v>5</v>
       </c>
       <c r="L35" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="M35" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="N35" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="P35" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="Q35" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="R35" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S35">
         <v>4</v>
       </c>
       <c r="T35" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="U35" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="V35" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="W35" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="X35" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.3">
@@ -3557,67 +3557,67 @@
         <v>46007.714942129598</v>
       </c>
       <c r="D36" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="F36" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G36" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H36" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="K36">
         <v>3</v>
       </c>
       <c r="L36" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="M36" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="N36" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="Q36" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="R36" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="S36">
         <v>3</v>
       </c>
       <c r="T36" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="U36" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="V36" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W36" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="X36" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.3">
@@ -3631,67 +3631,67 @@
         <v>46007.809212963002</v>
       </c>
       <c r="D37" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="F37" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G37" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H37" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="K37">
         <v>3</v>
       </c>
       <c r="L37" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="M37" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="N37" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="Q37" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="R37" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S37">
         <v>5</v>
       </c>
       <c r="T37" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="U37" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="V37" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="W37" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="X37" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.3">
@@ -3705,64 +3705,64 @@
         <v>46007.821875000001</v>
       </c>
       <c r="D38" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="F38" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G38" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="K38">
         <v>4</v>
       </c>
       <c r="L38" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="M38" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="N38" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="Q38" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="R38" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S38">
         <v>3</v>
       </c>
       <c r="T38" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="U38" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="V38" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W38" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="X38" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.3">
@@ -3776,67 +3776,67 @@
         <v>46007.862233796302</v>
       </c>
       <c r="D39" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="F39" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G39" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H39" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="K39">
         <v>3</v>
       </c>
       <c r="L39" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="M39" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="N39" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="Q39" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="R39" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="S39">
         <v>4</v>
       </c>
       <c r="T39" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="U39" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="V39" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="W39" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="X39" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.3">
@@ -3850,64 +3850,64 @@
         <v>46007.9205671296</v>
       </c>
       <c r="D40" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="F40" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G40" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="K40">
         <v>3</v>
       </c>
       <c r="L40" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="M40" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="N40" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="Q40" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="R40" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="S40">
         <v>4</v>
       </c>
       <c r="T40" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="U40" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="V40" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W40" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="X40" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.3">
@@ -3921,64 +3921,64 @@
         <v>46007.926608796297</v>
       </c>
       <c r="D41" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="F41" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G41" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="K41">
         <v>3</v>
       </c>
       <c r="L41" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="M41" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="N41" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="Q41" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="R41" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="S41">
         <v>5</v>
       </c>
       <c r="T41" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="U41" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="V41" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="W41" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="X41" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.3">
@@ -3992,64 +3992,64 @@
         <v>46007.939131944397</v>
       </c>
       <c r="D42" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="F42" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G42" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I42" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="J42" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="K42">
         <v>5</v>
       </c>
       <c r="L42" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="M42" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="N42" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O42" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="Q42" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="R42" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="S42">
         <v>3</v>
       </c>
       <c r="T42" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="U42" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="V42" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W42" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="X42" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.3">
@@ -4063,67 +4063,67 @@
         <v>46008.551817129599</v>
       </c>
       <c r="D43" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="F43" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G43" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H43" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="K43">
         <v>3</v>
       </c>
       <c r="L43" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="M43" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="N43" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="Q43" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="R43" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="S43">
         <v>4</v>
       </c>
       <c r="T43" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="U43" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="V43" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W43" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="X43" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.3">
@@ -4137,67 +4137,67 @@
         <v>46008.725729166697</v>
       </c>
       <c r="D44" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="F44" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G44" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H44" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I44" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="J44" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="K44">
         <v>3</v>
       </c>
       <c r="L44" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="M44" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="N44" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="P44" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="Q44" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="R44" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S44">
         <v>5</v>
       </c>
       <c r="T44" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="U44" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="V44" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W44" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="X44" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.3">
@@ -4211,67 +4211,67 @@
         <v>46008.798252314802</v>
       </c>
       <c r="D45" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F45" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G45" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H45" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="I45" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="J45" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="K45">
         <v>1</v>
       </c>
       <c r="L45" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="M45" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="N45" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="P45" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="Q45" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="R45" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S45">
         <v>4</v>
       </c>
       <c r="T45" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="U45" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="V45" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W45" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="X45" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.3">
@@ -4285,64 +4285,64 @@
         <v>46008.878078703703</v>
       </c>
       <c r="D46" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="F46" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G46" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I46" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="J46" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="K46">
         <v>3</v>
       </c>
       <c r="L46" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="M46" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="N46" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="P46" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="Q46" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="R46" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S46">
         <v>5</v>
       </c>
       <c r="T46" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="U46" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="V46" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W46" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="X46" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.3">
@@ -4356,64 +4356,64 @@
         <v>46009.515196759297</v>
       </c>
       <c r="D47" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="F47" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G47" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="K47">
         <v>3</v>
       </c>
       <c r="L47" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="M47" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="N47" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="O47" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="Q47" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="R47" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S47">
         <v>3</v>
       </c>
       <c r="T47" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="U47" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="V47" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="W47" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="X47" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.3">
@@ -4427,67 +4427,67 @@
         <v>46010.277303240699</v>
       </c>
       <c r="D48" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="F48" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G48" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="H48" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="K48">
         <v>2</v>
       </c>
       <c r="L48" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="M48" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="N48" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="Q48" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="R48" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="S48">
         <v>5</v>
       </c>
       <c r="T48" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="U48" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="V48" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W48" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="X48" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.3">
@@ -4501,64 +4501,64 @@
         <v>46011.116585648102</v>
       </c>
       <c r="D49" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="F49" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G49" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="K49">
         <v>5</v>
       </c>
       <c r="L49" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="M49" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="N49" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="Q49" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="R49" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S49">
         <v>1</v>
       </c>
       <c r="T49" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="U49" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="V49" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="W49" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="X49" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="1:24" x14ac:dyDescent="0.3">
@@ -4572,67 +4572,67 @@
         <v>46016.916400463</v>
       </c>
       <c r="D50" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="F50" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G50" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H50" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="K50">
         <v>4</v>
       </c>
       <c r="L50" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="M50" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="N50" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="Q50" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="R50" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S50">
         <v>3</v>
       </c>
       <c r="T50" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="U50" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="V50" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="W50" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="X50" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.3">
@@ -4646,64 +4646,64 @@
         <v>46027.278877314799</v>
       </c>
       <c r="D51" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="F51" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G51" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="K51">
         <v>3</v>
       </c>
       <c r="L51" t="s">
+        <v>27</v>
+      </c>
+      <c r="M51" t="s">
         <v>44</v>
       </c>
-      <c r="M51" t="s">
-        <v>61</v>
-      </c>
       <c r="N51" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="Q51" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="R51" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S51">
         <v>5</v>
       </c>
       <c r="T51" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="U51" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="V51" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="W51" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="X51" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.3">
@@ -4717,67 +4717,67 @@
         <v>46027.690671296303</v>
       </c>
       <c r="D52" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="F52" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G52" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H52" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="K52">
         <v>4</v>
       </c>
       <c r="L52" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="M52" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="N52" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="Q52" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="R52" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="S52">
         <v>4</v>
       </c>
       <c r="T52" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="U52" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="V52" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W52" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="X52" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:24" x14ac:dyDescent="0.3">
@@ -4791,67 +4791,67 @@
         <v>46028.062256944402</v>
       </c>
       <c r="D53" t="s">
+        <v>7</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F53" t="s">
+        <v>9</v>
+      </c>
+      <c r="G53" t="s">
+        <v>10</v>
+      </c>
+      <c r="H53" t="s">
+        <v>73</v>
+      </c>
+      <c r="I53" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E53" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F53" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" t="s">
-        <v>27</v>
-      </c>
-      <c r="H53" t="s">
-        <v>90</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="J53" s="2" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="K53">
         <v>5</v>
       </c>
       <c r="L53" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="M53" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="N53" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="Q53" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="R53" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S53">
         <v>3</v>
       </c>
       <c r="T53" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="U53" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="V53" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W53" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="X53" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54" spans="1:24" x14ac:dyDescent="0.3">
@@ -4865,67 +4865,67 @@
         <v>46034.819039351903</v>
       </c>
       <c r="D54" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="F54" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G54" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H54" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="K54">
         <v>2</v>
       </c>
       <c r="L54" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="M54" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="N54" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="Q54" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="R54" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="S54">
         <v>4</v>
       </c>
       <c r="T54" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="U54" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="V54" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W54" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="X54" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
     </row>
     <row r="55" spans="1:24" x14ac:dyDescent="0.3">
@@ -4939,67 +4939,67 @@
         <v>46038.335231481498</v>
       </c>
       <c r="D55" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="F55" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G55" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H55" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="K55">
         <v>3</v>
       </c>
       <c r="L55" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="M55" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="N55" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="Q55" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="R55" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S55">
         <v>5</v>
       </c>
       <c r="T55" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="U55" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="V55" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W55" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="X55" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:24" x14ac:dyDescent="0.3">
@@ -5013,64 +5013,64 @@
         <v>46039.740462962996</v>
       </c>
       <c r="D56" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="F56" t="s">
+        <v>9</v>
+      </c>
+      <c r="G56" t="s">
+        <v>11</v>
+      </c>
+      <c r="I56" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G56" t="s">
-        <v>28</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="J56" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="K56">
         <v>5</v>
       </c>
       <c r="L56" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="M56" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="N56" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="Q56" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="R56" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S56">
         <v>3</v>
       </c>
       <c r="T56" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="U56" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="V56" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="W56" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="X56" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
     </row>
     <row r="57" spans="1:24" x14ac:dyDescent="0.3">
@@ -5084,67 +5084,67 @@
         <v>46040.731504629599</v>
       </c>
       <c r="D57" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F57" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G57" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H57" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="K57">
         <v>3</v>
       </c>
       <c r="L57" t="s">
+        <v>27</v>
+      </c>
+      <c r="M57" t="s">
         <v>44</v>
       </c>
-      <c r="M57" t="s">
-        <v>61</v>
-      </c>
       <c r="N57" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="Q57" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="R57" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S57">
         <v>5</v>
       </c>
       <c r="T57" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="U57" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="V57" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W57" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="X57" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:24" x14ac:dyDescent="0.3">
@@ -5158,64 +5158,64 @@
         <v>46045.123402777797</v>
       </c>
       <c r="D58" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="F58" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G58" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="K58">
         <v>5</v>
       </c>
       <c r="L58" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="M58" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="N58" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="Q58" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="R58" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S58">
         <v>3</v>
       </c>
       <c r="T58" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="U58" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="V58" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W58" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="X58" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="59" spans="1:24" x14ac:dyDescent="0.3">
@@ -5229,67 +5229,67 @@
         <v>46049.746273148099</v>
       </c>
       <c r="D59" t="s">
+        <v>7</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E59" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="F59" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G59" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H59" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I59" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="J59" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="K59">
         <v>2</v>
       </c>
       <c r="L59" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="M59" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="N59" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="P59" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="Q59" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="R59" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S59">
         <v>5</v>
       </c>
       <c r="T59" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="U59" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="V59" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="W59" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="X59" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.3">
@@ -5303,67 +5303,67 @@
         <v>46050.1848032407</v>
       </c>
       <c r="D60" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="F60" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G60" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H60" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="K60">
         <v>4</v>
       </c>
       <c r="L60" t="s">
+        <v>27</v>
+      </c>
+      <c r="M60" t="s">
         <v>44</v>
       </c>
-      <c r="M60" t="s">
-        <v>61</v>
-      </c>
       <c r="N60" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="P60" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>17</v>
+      </c>
+      <c r="R60" t="s">
         <v>55</v>
-      </c>
-      <c r="Q60" t="s">
-        <v>34</v>
-      </c>
-      <c r="R60" t="s">
-        <v>72</v>
       </c>
       <c r="S60">
         <v>4</v>
       </c>
       <c r="T60" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="U60" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="V60" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W60" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="X60" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
